--- a/_FACTORY/_LIGNES/_TEMPLATE/A4_POOLS/A4_THEME.xlsx
+++ b/_FACTORY/_LIGNES/_TEMPLATE/A4_POOLS/A4_THEME.xlsx
@@ -1123,10 +1123,14 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>[non trouvé dans glossaire — vérifier source]</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr"/>
+          <t>Comportement obligatoire de signalement des opportunités de réduction de tokens avant chaque action ou tool call.</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>[RULE-TOKEN-MONITOR-001] CLAUDE SIGNALE CHAQUE OPPORTUNITÉ TOKEN — comportement obligatoire, tous contextes.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -1143,26 +1147,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>MANQUANT</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>TOKEN_OPTIMIZATION_MONITORING — présent dans config step mais absent du glossaire</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>→ Ajouter dans glossaire_documentaire_factory.md</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Aucune alerte automatique — vérification manuelle recommandée à chaque étape</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-19</t>
+          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-21</t>
         </is>
       </c>
     </row>

--- a/_FACTORY/_LIGNES/_TEMPLATE/A4_POOLS/A4_THEME.xlsx
+++ b/_FACTORY/_LIGNES/_TEMPLATE/A4_POOLS/A4_THEME.xlsx
@@ -10,7 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="POOLS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASSIGNATIONS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONTROLE_STOCKS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLOSSAIRE" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -522,170 +521,156 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>POOL_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>POSITION_QUIZ</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CIBLE_NIVEAU</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>THÈME_ÉDITORIAL</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>THEME_EDITORIAL</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>MODE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>SOUS_THÈMES</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ITEMS_ASSIGNÉS</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SOUS_THEMES</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ITEMS_ASSIGNES</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>STOCK_CIBLE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>STOCK_ACTUEL</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>SIGNAL_RUNTIME</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>FAISABILITE</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>QV-01</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>QV</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>[Thème du pool]</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>SIMPLE / AGRÉGÉ</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="n">
+      <c r="I2" t="n">
         <v>15</v>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>IF-SF-01</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>IF-SF</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>[Thème finale SF]</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>SIMPLE</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="n">
+      <c r="I3" t="n">
         <v>12</v>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>IF-ROT-01</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>IF-ROT</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Q20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>[Thème rotation]</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>SIMPLE</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="n">
+      <c r="I4" t="n">
         <v>10</v>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -841,333 +826,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>GLOSSAIRE — ÉTAPE A4</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Source : glossaire_documentaire_factory.md — LECTURE SEULE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>TERME</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>DÉFINITION COURTE</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>RÈGLE PRINCIPALE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Unité opérationnelle contenant un stock de questions CONSISTENCY_VALIDATED.</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>IF_SF</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Pool d'incontournables semi-fixes.</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-IFS-001] Les angles IF-SF ne peuvent pas être réutilisés dans les QV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>IF_ROT</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Pool d'incontournables rotatifs.</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-IFR-001] Les angles IF-ROT sont interdits dans les QV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>QV</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Questions Variables.</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-QV-001] Les QV doivent maximiser la diversité documentaire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>POOLS_ARCHITECTURE</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Définition des 20 pools opérationnels (IF-SF, IF-ROT, QV) avec assignations angles et quotas.</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-POOLS-ARCH-001] Exactement 20 pools obligatoire. Tous angles ANGIPREGEN assignés.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>POOLS_DOC</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Document définissant les pools opérationnels du quiz.</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>POOL_COLLISION</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Réutilisation problématique d'un même angle dans plusieurs pools.</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>ROTATION_LENTE</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Renouvellement inférieur à 10 % des questions par export.</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>ROTATION_RAPIDE</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Renouvellement supérieur à 40 % des questions par export.</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>FORTE_VARIETE</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Présence d'au moins 12 sous-thèmes distincts dans les pools QV.</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>ONBOARDING_FLUIDE</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Présence d'au moins 3 questions N1 dans les 5 premières questions d'une partie.</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>ANGLE_ASSIGNMENT</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Assignation explicite d'un angle à un pool unique.</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-ANGLE-002] Un angle assigné à un pool est interdit dans les autres pools.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>COHERENCE_CULTURELLE</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Absence de contradiction chronologique, thématique ou factuelle dans un même quiz.</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-COH-001] La CONSISTENCY culturelle prime sur les quotas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>STATUS_STANDARD</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Liste officielle des statuts documentaires autorisés.</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-STATUS-001] Tout autre format de statut est interdit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>MACHINE_READABLE</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Bloc structuré destiné à être interprété directement par une IA.</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-MACHINE-001] Les données structurelles critiques doivent exister en version MACHINE_READABLE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>TOKEN_OPTIMIZATION_MONITORING</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Comportement obligatoire de signalement des opportunités de réduction de tokens avant chaque action ou tool call.</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>[RULE-TOKEN-MONITOR-001] CLAUDE SIGNALE CHAQUE OPPORTUNITÉ TOKEN — comportement obligatoire, tous contextes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>⚠ ALERTES — TERMES POTENTIELLEMENT MANQUANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>L'IA consigne ici tout terme utilisé dans cette étape mais absent du glossaire source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Aucune alerte automatique — vérification manuelle recommandée à chaque étape</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-21</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>